--- a/Docs/Global Technology Fund A-acc-EUR-Moviment.xlsx
+++ b/Docs/Global Technology Fund A-acc-EUR-Moviment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\_Actiu\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAD4C5B-9449-4C9B-8027-33B664BDA7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B8CE0B-6E11-47D6-AFE7-ED93FDD4920A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{BBEA0039-8FB1-4B67-9ED2-8CEE43EB059B}"/>
+    <workbookView xWindow="22932" yWindow="0" windowWidth="23256" windowHeight="12576" xr2:uid="{BBEA0039-8FB1-4B67-9ED2-8CEE43EB059B}"/>
   </bookViews>
   <sheets>
     <sheet name="Moviments" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="58">
   <si>
     <t>Traspàs C</t>
   </si>
@@ -174,6 +174,33 @@
   </si>
   <si>
     <t>PiG vend R</t>
+  </si>
+  <si>
+    <t>173 en cartera</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>173 venda real</t>
+  </si>
+  <si>
+    <t>PiG Total</t>
+  </si>
+  <si>
+    <t>Import compra Orig</t>
+  </si>
+  <si>
+    <t>Vend 1251</t>
+  </si>
+  <si>
+    <t>PiG venda 1251</t>
+  </si>
+  <si>
+    <t>PiG venda 1279</t>
   </si>
 </sst>
 </file>
@@ -188,7 +215,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="#,##0.000\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +227,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -225,7 +266,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -339,11 +380,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -431,7 +483,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1144,7 +1228,7 @@
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J13" s="39" t="s">
         <v>39</v>
       </c>
@@ -1161,18 +1245,33 @@
         <v>31602.735601000004</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="F14" s="16"/>
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D14" s="64"/>
+      <c r="E14" s="74" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="75">
+        <f>D8*(E8-E2)</f>
+        <v>4654.7999999999993</v>
+      </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="F15" s="16"/>
+    <row r="15" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D15" s="64"/>
+      <c r="E15" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="75">
+        <f>D11*(E11-E2)</f>
+        <v>634.99999999999989</v>
+      </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="F16" s="16"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2268,21 +2367,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6857271D-36C8-497E-BC31-A84854D64CE5}">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.54296875" customWidth="1"/>
     <col min="2" max="2" width="4.90625" customWidth="1"/>
     <col min="3" max="3" width="4.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.1796875" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" customWidth="1"/>
     <col min="6" max="6" width="9.6328125" customWidth="1"/>
     <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.6328125" customWidth="1"/>
     <col min="10" max="11" width="8.81640625" customWidth="1"/>
     <col min="12" max="12" width="10.453125" customWidth="1"/>
-    <col min="13" max="14" width="11.453125" customWidth="1"/>
+    <col min="13" max="13" width="11.81640625" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="16" width="8.81640625" customWidth="1"/>
     <col min="17" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.7265625" bestFit="1" customWidth="1"/>
@@ -2493,7 +2593,7 @@
       <c r="G5" s="25">
         <v>1065.5911000000001</v>
       </c>
-      <c r="H5" s="53">
+      <c r="H5" s="25">
         <f>SUM(H6:H10)</f>
         <v>1065.5911000000001</v>
       </c>
@@ -3200,31 +3300,19 @@
     </row>
     <row r="21" spans="1:18" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="7"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="43"/>
-      <c r="F21" s="44"/>
       <c r="K21" s="27"/>
       <c r="L21" s="30" t="s">
         <v>31</v>
       </c>
       <c r="M21" s="31"/>
       <c r="N21" s="27"/>
+      <c r="P21" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q21" s="44"/>
     </row>
     <row r="22" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B22" s="7"/>
-      <c r="C22" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="46"/>
       <c r="K22" s="27"/>
       <c r="L22" s="32" t="s">
         <v>48</v>
@@ -3234,21 +3322,16 @@
         <v>6715.3807197918886</v>
       </c>
       <c r="N22" s="27"/>
+      <c r="P22" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q22" s="54">
+        <f>M11</f>
+        <v>1593.4276759886566</v>
+      </c>
     </row>
     <row r="23" spans="1:18" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="7"/>
-      <c r="C23" s="47">
-        <v>16</v>
-      </c>
-      <c r="D23" s="5">
-        <f>I5/G5*H10</f>
-        <v>132.83336379762375</v>
-      </c>
-      <c r="E23" s="48">
-        <f>D23*P5</f>
-        <v>2425.5372227602638</v>
-      </c>
-      <c r="F23" s="46"/>
       <c r="K23" s="27"/>
       <c r="L23" s="32" t="s">
         <v>33</v>
@@ -3258,21 +3341,16 @@
         <v>5693.6402770113509</v>
       </c>
       <c r="N23" s="27"/>
+      <c r="P23" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q23" s="54">
+        <f>K11*O19</f>
+        <v>7287.0679530000079</v>
+      </c>
     </row>
     <row r="24" spans="1:18" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="7"/>
-      <c r="C24" s="47">
-        <v>17</v>
-      </c>
-      <c r="D24" s="5">
-        <f>I11/G11*H12</f>
-        <v>5.9313828886628102</v>
-      </c>
-      <c r="E24" s="48">
-        <f>D24*P11</f>
-        <v>117.38205744784817</v>
-      </c>
-      <c r="F24" s="46"/>
       <c r="K24" s="27"/>
       <c r="L24" s="37" t="s">
         <v>26</v>
@@ -3282,20 +3360,139 @@
         <v>12409.02099680324</v>
       </c>
       <c r="N24" s="27"/>
+      <c r="P24" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="57">
+        <f>+Q23-Q22</f>
+        <v>5693.6402770113509</v>
+      </c>
     </row>
     <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C25" s="49"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="51">
-        <f>SUM(E23:E24)</f>
+      <c r="N25" s="27"/>
+      <c r="P25" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q25" s="44"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K26" s="61"/>
+      <c r="L26" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="M26" s="63"/>
+      <c r="N26" s="27"/>
+      <c r="P26" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="54">
+        <f>Q5+Q11</f>
         <v>2542.919280208112</v>
       </c>
-      <c r="F25" s="52"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="K27" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="N27" s="27"/>
+      <c r="P27" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q27" s="54">
+        <f>+Q10+Q12</f>
+        <v>9258.3000000000011</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K28" s="47">
+        <v>16</v>
+      </c>
+      <c r="L28" s="70">
+        <f>J10</f>
+        <v>132.83336379762375</v>
+      </c>
+      <c r="M28" s="71">
+        <f>L28*P5</f>
+        <v>2425.5372227602638</v>
+      </c>
+      <c r="N28" s="27"/>
+      <c r="P28" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28" s="57">
+        <f>+Q27-Q26</f>
+        <v>6715.3807197918886</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K29" s="47">
+        <v>17</v>
+      </c>
+      <c r="L29" s="70">
+        <f>J12</f>
+        <v>5.9313828886628102</v>
+      </c>
+      <c r="M29" s="71">
+        <f>L29*P11</f>
+        <v>117.38205744784817</v>
+      </c>
+      <c r="N29" s="27"/>
+      <c r="P29" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q29" s="59">
+        <f>Q24+Q28</f>
+        <v>12409.02099680324</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K30" s="58"/>
+      <c r="L30" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="38">
+        <f>SUM(M28:M29)</f>
+        <v>2542.919280208112</v>
+      </c>
+      <c r="N30" s="27"/>
+    </row>
+    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K31" s="66" t="s">
+        <v>55</v>
+      </c>
+      <c r="L31" s="43">
+        <f>H12+H10</f>
+        <v>270</v>
+      </c>
+      <c r="M31" s="72">
+        <f>L31*O12</f>
+        <v>9258.2999999999993</v>
+      </c>
+      <c r="N31" s="27"/>
+      <c r="Q31" s="8"/>
+    </row>
+    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K32" s="67"/>
+      <c r="L32" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="38">
+        <f>M31-M30</f>
+        <v>6715.3807197918868</v>
+      </c>
+      <c r="N32" s="27"/>
+    </row>
+    <row r="33" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N33" s="27"/>
+    </row>
+    <row r="34" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N34" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
